--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +89,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5964136.675178966</v>
+        <v>6635036.072025659</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>6032353.637951385</v>
+        <v>6703253.034798077</v>
       </c>
     </row>
     <row r="8">
@@ -600,7 +602,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5964136.675178966</v>
+        <v>6635036.072025659</v>
       </c>
     </row>
     <row r="20">
@@ -616,7 +618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>2618163.484356981</v>
+        <v>3289062.881203674</v>
       </c>
     </row>
     <row r="23">
@@ -651,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05T11:08:08+00:00</t>
+          <t>2026-06-08T08:17:50+00:00</t>
         </is>
       </c>
     </row>
@@ -678,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -986,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>872445.7139206566</v>
+        <v>812834.4526901663</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>872445.7139206566</v>
+        <v>812834.4526901663</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>121025.8463851794</v>
+        <v>180637.1076156697</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1051,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>849246.5854319996</v>
+        <v>791220.4420908991</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>849246.5854319996</v>
+        <v>791220.4420908991</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-594448.3847994745</v>
+        <v>-536422.2414583738</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1116,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>435549.3759310356</v>
+        <v>405789.7619938833</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>435549.3759310356</v>
+        <v>405789.7619938833</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>60419.49776761026</v>
+        <v>90179.11170476262</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1181,13 +1183,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>343171.407399411</v>
+        <v>319723.6672284029</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>343171.407399411</v>
+        <v>319723.6672284029</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>109933.892600589</v>
+        <v>133381.6327715972</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1246,13 +1248,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>254217.4736231126</v>
+        <v>236847.6545183782</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>254217.4736231126</v>
+        <v>236847.6545183782</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>3014859.71515192</v>
+        <v>3032229.534256655</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1265,59 +1267,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galaxy Arch CLO Token (GACLO-1)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>49900000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>46308344.52</v>
+        <v>100275383.2182718</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-3591655.48</v>
+        <v>100275383.2182718</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>389109.9</v>
+        <v>272574.4768466928</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>389109.9</v>
+        <v>272574.4768466928</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>50000000</v>
+        <v>72582681.53814024</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>169038.5113926973</v>
+        <v>228619.0175110952</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>169038.5113926973</v>
+        <v>228619.0175110952</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>220071.3886073027</v>
+        <v>43955.45933559752</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1325,26 +1327,22 @@
       <c r="R9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>(off-chain notional)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
+          <t>Galaxy Arch CLO Token (GACLO-1)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>plume</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1353,40 +1351,40 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>50865822.2173752</v>
+        <v>49900000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>46308344.52</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-18126183.27598623</v>
+        <v>-3591655.48</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-48513.80302671796</v>
+        <v>389109.9</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-48513.80302671796</v>
+        <v>389109.9</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>39202809.65417551</v>
+        <v>50000000</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>132535.6917270618</v>
+        <v>157488.6823318605</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>132535.6917270618</v>
+        <v>157488.6823318605</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>-181049.4947537798</v>
+        <v>231621.2176681395</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1394,64 +1392,68 @@
       <c r="R10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>(off-chain notional)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
+          <t>Anemoy Tokenized Apollo Diversified Credit Fund (ACRDX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>plume</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>25025948.067729</v>
+        <v>50865822.2173752</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>25037160.415677</v>
+        <v>32739638.94138896</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>11212.347948</v>
+        <v>-18126183.27598623</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>11212.347948</v>
+        <v>-48513.80302671796</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>11212.347948</v>
+        <v>-48513.80302671796</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>25025948.067729</v>
+        <v>39202809.65417551</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>84606.98015119717</v>
+        <v>123479.9767228568</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>84606.98015119717</v>
+        <v>123479.9767228568</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-73394.63220319718</v>
+        <v>-171993.7797495748</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1464,12 +1466,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Curve AUSD/USDC stableswap LP</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1483,40 +1485,40 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>25001164.10540737</v>
+        <v>25025948.067729</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>25001443.90695427</v>
+        <v>25037160.415677</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>279.8015468940151</v>
+        <v>11212.347948</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>279.8015468940151</v>
+        <v>11212.347948</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>279.8015468940151</v>
+        <v>11212.347948</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25001164.10540737</v>
+        <v>25025948.067729</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>84523.19126925195</v>
+        <v>78826.07170584421</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>84523.19126925195</v>
+        <v>78826.07170584421</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-84243.38972235794</v>
+        <v>-67613.7237578442</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1529,12 +1531,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
+          <t>Curve AUSD/USDC stableswap LP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1544,44 +1546,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>24982367.8949618</v>
+        <v>25001164.10540737</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>25056434.04308184</v>
+        <v>25001443.90695427</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>74066.14812003903</v>
+        <v>279.8015468940151</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>74066.14812003903</v>
+        <v>279.8015468940151</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>74066.14812003903</v>
+        <v>279.8015468940151</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>24982367.8949618</v>
+        <v>25001164.10540737</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>84459.64560058111</v>
+        <v>78748.0078344643</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>84459.64560058111</v>
+        <v>78748.0078344643</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-10393.49748054208</v>
+        <v>-78468.20628757028</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1594,12 +1596,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
+          <t>Grove x Steakhouse AUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1613,40 +1615,40 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5004060.193602587</v>
+        <v>24982367.8949618</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>9022511.56296834</v>
+        <v>25056434.04308184</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>4018451.369365753</v>
+        <v>74066.14812003903</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>18294.20342186725</v>
+        <v>74066.14812003903</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>18294.20342186725</v>
+        <v>74066.14812003903</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>5713765.679339128</v>
+        <v>24982367.8949618</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>19316.9288976434</v>
+        <v>78688.8040261462</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>19316.9288976434</v>
+        <v>78688.8040261462</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-1022.725475776144</v>
+        <v>-4622.655906107168</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1659,12 +1661,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Grove x Steakhouse USDC (Morpho 4626)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1674,44 +1676,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>5004060.193602587</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>9022511.56296834</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>4018451.369365753</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>5.6e-09</v>
+        <v>18294.20342186725</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>5.6e-09</v>
+        <v>18294.20342186725</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>3966608.499661189</v>
+        <v>5713765.679339128</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>13410.19192120695</v>
+        <v>17997.06855984254</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>13410.19192120695</v>
+        <v>17997.06855984254</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>-13410.19192120135</v>
+        <v>297.1348620247136</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1724,59 +1726,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1010849.948509241</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1014520.901611681</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3670.953102440081</v>
+        <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3670.953102440081</v>
+        <v>5.6e-09</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3670.953102440081</v>
+        <v>5.6e-09</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1010849.948509241</v>
+        <v>3966608.499661189</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>3417.451410747734</v>
+        <v>12493.91891875997</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>3417.451410747734</v>
+        <v>12493.91891875997</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>253.5016916923468</v>
+        <v>-12493.91891875437</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1789,59 +1791,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>Grove x Steakhouse USDC High Yield (Base, Morpho 4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>1010849.948509241</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>1014520.901611681</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>3670.953102440081</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>3670.953102440081</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>3670.953102440081</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>10068.978846</v>
+        <v>1010849.948509241</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>34.04090390744798</v>
+        <v>3183.948528518986</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>34.04090390744798</v>
+        <v>3183.948528518986</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-34.04090390744798</v>
+        <v>487.0045739210946</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1854,12 +1856,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1869,44 +1871,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.3672154333303549</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.3672154333303549</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.001241471004211749</v>
+        <v>31.71500421767835</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.001241471004211749</v>
+        <v>31.71500421767835</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-0.0005870729925121763</v>
+        <v>-31.71500421767835</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1919,12 +1921,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1938,40 +1940,40 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3672154333303549</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3672154333303549</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>3.380770227853945e-09</v>
+        <v>0.001156645494542415</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>3.380770227853945e-09</v>
+        <v>0.001156645494542415</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-3.380770227853945e-09</v>
+        <v>-0.0005022474828428421</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1984,12 +1986,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1999,14 +2001,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -2024,19 +2026,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>3.14977364663721e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0</v>
+        <v>3.14977364663721e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0</v>
+        <v>-3.14977364663721e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2049,12 +2051,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2064,7 +2066,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -2114,12 +2116,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2129,26 +2131,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
@@ -2166,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0</v>
@@ -2179,12 +2181,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2201,19 +2203,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0</v>
@@ -2231,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>
@@ -2244,12 +2246,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2309,12 +2311,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2352,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0</v>
@@ -2369,21 +2371,17 @@
       <c r="R25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2393,7 +2391,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
@@ -2421,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2438,17 +2436,21 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2508,12 +2510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2523,7 +2525,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -2573,17 +2575,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2634,6 +2636,197 @@
         <v>0</v>
       </c>
       <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USDC raw on Base (ALM idle)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>398324.92</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>398324.92</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>398324.92</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PSM_CURVE_DEDUCT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3075,6 +3268,1671 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3181207993.751286</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2157378356.185151</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1023829637.566135</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>102789.3825737967</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>332400.8238442471</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3181207993.751286</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2157378356.185151</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1023829637.566135</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>102789.3825737967</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>332400.8238442471</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3181207993.751286</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2157378356.185151</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1023829637.566135</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>102789.3825737967</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>332400.8238442471</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3131188095.712601</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2107995728.578282</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1023192367.134319</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>103161.7812172811</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>327517.3913693619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3081184251.809235</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2108176318.298201</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>973007933.5110337</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>97975.47676751614</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>322195.4437217471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3082184251.809235</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2108380391.252974</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>973803860.5562611</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>98055.62136761917</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>322301.8744925075</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3082184251.809235</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2108587094.329367</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>973597157.4798684</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>98034.80773212721</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>322301.8744925075</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3131184327.976176</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2108788245.613199</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1022396082.362976</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>103077.0320153224</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>327516.9903662701</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3131184327.976176</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2108788245.613199</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1022396082.362976</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>103077.0320153224</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>327516.9903662701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>3131184327.976176</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-2.980232238769531e-08</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2108788245.613199</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1022396082.362976</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>103077.0320153224</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>327516.9903662701</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3148116029.450206</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2059385339.259129</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1088730690.191077</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>110137.0754545517</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>329319.0444044351</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3125114749.761749</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2059556797.052049</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1065557952.7097</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>107670.7831437818</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>326871.0004787185</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3098127250.207238</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2009741160.351841</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1088386089.855397</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>110100.399375221</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>323998.7001002377</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>3049133870.855949</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1959927297.217484</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1089206573.638465</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>110187.7240966493</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>318784.2969737265</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3024125399.936529</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1910113487.975783</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1114011911.960746</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>112827.7753732605</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>316122.6261382353</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3024125399.936529</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1910113487.975783</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1114011911.960746</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>112827.7753732605</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>316122.6261382353</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3024125399.936529</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1910113487.975783</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1114011911.960746</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.03743491707043663</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>112827.7753732605</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>316122.6261382353</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3024125399.936529</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1860660881.766952</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1163464518.169577</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>117650.8305414484</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>315682.4023115099</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2927122353.803659</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1810853021.191645</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1116269332.612014</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>112627.8105663799</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>305358.2933454882</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2857131781.923406</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1761032914.681363</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1096098867.242043</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>110481.0523904593</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>297909.1428343162</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2811136939.007828</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1711214017.535519</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1099922921.472309</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>110888.0494296158</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>293013.8762518107</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2757146240.743185</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1661341147.920374</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1095805092.822811</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>110449.7857525907</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>287267.6046216161</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2758146240.743185</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>1661341147.920374</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1096805092.822811</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>110556.2165233511</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>287374.0353923764</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2760146240.743185</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1661341147.920374</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1098805092.822811</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>110769.0780648717</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>287586.8969338971</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2763146240.743185</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1661657204.096318</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1101489036.646868</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.03650000241537366</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.03960950242261978</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.03726825040376996</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>111054.7322747435</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>287906.1892461781</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2712152913.865112</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>1611942678.208152</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1100210235.65696</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>110565.3447970185</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>279994.5331871066</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2664162487.280517</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1562079744.442469</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1102082742.838048</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>110762.1615797958</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>274950.3221635728</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2647157440.00387</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>1562219774.21512</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1084937665.78875</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>108960.0649366465</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>273162.9438668333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2652157440.00387</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>1562287682.63512</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1089869757.36875</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>109478.4706372722</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>273688.4873327413</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2657157440.00387</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1562287682.63512</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1094869757.36875</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>110004.0141031801</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>274214.0307986492</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2660157440.00387</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>-1.490116119384766e-08</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>1562287682.63512</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>1097869757.36875</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.03600000425292382</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0.03910800426568259</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.03718466737761376</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>110319.3401827249</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>274529.356878194</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="n">
+        <v>3345973.190821985</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>9534049.062243789</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08T08:17:50+00:00</t>
+          <t>2026-06-09T00:23:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6635036.072025659</v>
+        <v>3635291.947968574</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>68216.96277241873</v>
+        <v>71960.5970815084</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>6703253.034798077</v>
+        <v>3707252.545050082</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>6635036.072025659</v>
+        <v>3635291.947968574</v>
       </c>
     </row>
     <row r="20">
@@ -618,7 +618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>3289062.881203674</v>
+        <v>289318.7571465889</v>
       </c>
     </row>
     <row r="23">
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T00:23:16+00:00</t>
+          <t>2026-06-09T16:55:14+00:00</t>
         </is>
       </c>
     </row>
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>812834.4526901663</v>
+        <v>812760.4168600863</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>812834.4526901663</v>
+        <v>812760.4168600863</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>180637.1076156697</v>
+        <v>180711.1434457497</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1053,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>791220.4420908991</v>
+        <v>791148.3749411706</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>791220.4420908991</v>
+        <v>791148.3749411706</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-536422.2414583738</v>
+        <v>-536350.1743086454</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>405789.7619938833</v>
+        <v>405752.8012305104</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>405789.7619938833</v>
+        <v>405752.8012305104</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>90179.11170476262</v>
+        <v>90216.07246813549</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>319723.6672284029</v>
+        <v>319694.5456686299</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>319723.6672284029</v>
+        <v>319694.5456686299</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>133381.6327715972</v>
+        <v>133410.7543313701</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1230,31 +1230,31 @@
         <v>35270624.94365972</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>3269077.188775033</v>
+        <v>269333.0647179479</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3269077.188775033</v>
+        <v>269333.0647179479</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>75195134.98096719</v>
+        <v>75291900.92045291</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>236847.6545183782</v>
+        <v>237130.8446429374</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>236847.6545183782</v>
+        <v>237130.8446429374</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>3032229.534256655</v>
+        <v>32202.22007501045</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>228619.0175110952</v>
+        <v>228598.1940842861</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>228619.0175110952</v>
+        <v>228598.1940842861</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>43955.45933559752</v>
+        <v>43976.28276240663</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>157488.6823318605</v>
+        <v>157474.3377069666</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>157488.6823318605</v>
+        <v>157474.3377069666</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231621.2176681395</v>
+        <v>231635.5622930334</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>123479.9767228568</v>
+        <v>123468.7297308713</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>123479.9767228568</v>
+        <v>123468.7297308713</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-171993.7797495748</v>
+        <v>-171982.5327575893</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>78826.07170584421</v>
+        <v>78818.89194909131</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>78826.07170584421</v>
+        <v>78818.89194909131</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67613.7237578442</v>
+        <v>-67606.5440010913</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>78748.0078344643</v>
+        <v>78740.83518804425</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>78748.0078344643</v>
+        <v>78740.83518804425</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78468.20628757028</v>
+        <v>-78461.03364115024</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>78688.8040261462</v>
+        <v>78681.63677221791</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>78688.8040261462</v>
+        <v>78681.63677221791</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-4622.655906107168</v>
+        <v>-4615.488652178891</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17997.06855984254</v>
+        <v>17995.42932333451</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17997.06855984254</v>
+        <v>17995.42932333451</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>297.1348620247136</v>
+        <v>298.7740985327452</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>12493.91891875997</v>
+        <v>12492.78092853941</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>12493.91891875997</v>
+        <v>12492.78092853941</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-12493.91891875437</v>
+        <v>-12492.7809285338</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1837,13 +1837,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3183.948528518986</v>
+        <v>3183.658523252279</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3183.948528518986</v>
+        <v>3183.658523252279</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>487.0045739210946</v>
+        <v>487.2945791878016</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.71500421767835</v>
+        <v>31.71211550318614</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.71500421767835</v>
+        <v>31.71211550318614</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.71500421767835</v>
+        <v>-31.71211550318614</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001156645494542415</v>
+        <v>0.001156540143189488</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001156645494542415</v>
+        <v>0.001156540143189488</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0005022474828428421</v>
+        <v>-0.0005021421314899149</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2032,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.14977364663721e-09</v>
+        <v>3.149486754139332e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.14977364663721e-09</v>
+        <v>3.149486754139332e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.14977364663721e-09</v>
+        <v>-3.149486754139332e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:14+00:00</t>
+          <t>2026-06-09T22:25:25+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:25+00:00</t>
+          <t>2026-06-09T23:12:32+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:32+00:00</t>
+          <t>2026-06-10T10:52:08+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:08+00:00</t>
+          <t>2026-06-10T15:01:24+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -84,12 +85,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -653,7 +656,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T15:01:24+00:00</t>
+          <t>2026-06-23T21:34:42+00:00</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2854,185 +2857,367 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>3345973.190821985</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>5242531.28537233</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1070796625.540224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>8588504.476194315</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>997432546.824102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>73364078.71612211</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.03951024672617314</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (tbill_3m), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.03689032258064516</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>9534049.062243789</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0.03732734186107307</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>3345973.190821985</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.03747483383441957</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-6188075.871421805</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>-20.35412891753571</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>178277.9868267714</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3524251.177648756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3345973.190821985</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>178277.9868267714</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ramp_months</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>24</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ref_rate_kind</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tbill_3m</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>997432546.824102</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3104672.504638677</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>73364078.71612211</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>241300.6861833077</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3345973.190821985</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5242531.28537233</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>8588504.476194315</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>9534049.062243789</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>3345973.190821985</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-6188075.871421805</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ramp_months</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ref_rate_kind</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tbill_3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>4 (SoM) → 4 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -3296,7 +3481,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4898,7 +5083,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Σ daily charges</t>
         </is>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,168 +505,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>3707252.545050082</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>20518.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>3727771.065050082</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>3345973.190821985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3345973.190821985</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>5242531.28537233</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>8588504.476194315</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>3345973.190821985</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3345973.190821985</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-6188075.871421805</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>9534049.062243789</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>3635291.947968574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3635291.947968574</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-3345973.190821985</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>289318.7571465889</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-01 → 2026-05-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=86865826, base=46741326, ethereum=25218797, monad=78309381, plume=71786194</t>
+          <t>2026-05-01 → 2026-05-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23T21:34:42+00:00</t>
+          <t>avalanche_c=86865826, base=46741326, ethereum=25218797, monad=78309381, plume=71786194</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-23T22:22:01+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-23T22:22:01+00:00</t>
+          <t>2026-07-03T06:32:37+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-03T06:32:37+00:00</t>
+          <t>2026-07-07T14:51:43+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3635291.947968574</v>
+        <v>3585695.947968568</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>3727771.065050082</v>
+        <v>3678175.065050077</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3635291.947968574</v>
+        <v>3585695.947968568</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>289318.7571465889</v>
+        <v>239722.7571465833</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:43+00:00</t>
+          <t>2026-07-10T11:17:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>812760.4168600863</v>
+        <v>812729.8191806873</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>812760.4168600863</v>
+        <v>812729.8191806873</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>180711.1434457497</v>
+        <v>180741.7411251486</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>791148.3749411706</v>
+        <v>791118.590882017</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>791148.3749411706</v>
+        <v>791118.590882017</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-536350.1743086454</v>
+        <v>-536320.3902494919</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>405752.8012305104</v>
+        <v>405737.526010569</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>405752.8012305104</v>
+        <v>405737.526010569</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>90216.07246813549</v>
+        <v>90231.34768807696</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>319694.5456686299</v>
+        <v>319682.5102507983</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>319694.5456686299</v>
+        <v>319682.5102507983</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>133410.7543313701</v>
+        <v>133422.7897492017</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>237130.8446429374</v>
+        <v>237121.9174690625</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>237130.8446429374</v>
+        <v>237121.9174690625</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>32202.22007501045</v>
+        <v>32211.14724888539</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>228598.1940842861</v>
+        <v>228589.5881358311</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>228598.1940842861</v>
+        <v>228589.5881358311</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>43976.28276240663</v>
+        <v>43984.88871086163</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>157474.3377069666</v>
+        <v>157468.4093310286</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>157474.3377069666</v>
+        <v>157468.4093310286</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231635.5622930334</v>
+        <v>231641.4906689714</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>123468.7297308713</v>
+        <v>123464.0815510022</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>123468.7297308713</v>
+        <v>123464.0815510022</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-171982.5327575893</v>
+        <v>-171977.8845777201</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>78818.89194909131</v>
+        <v>78815.92468452427</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>78818.89194909131</v>
+        <v>78815.92468452427</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67606.5440010913</v>
+        <v>-67603.57673652428</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>78740.83518804425</v>
+        <v>78737.87086205014</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>78740.83518804425</v>
+        <v>78737.87086205014</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78461.03364115024</v>
+        <v>-78458.06931515611</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>78681.63677221791</v>
+        <v>78678.67467484385</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>78681.63677221791</v>
+        <v>78678.67467484385</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-4615.488652178891</v>
+        <v>-4612.526554804812</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17995.42932333451</v>
+        <v>17994.75185631512</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17995.42932333451</v>
+        <v>17994.75185631512</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>298.7740985327452</v>
+        <v>299.4515655521261</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1767,31 +1767,31 @@
         <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5.6e-09</v>
+        <v>-4e-21</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>5.6e-09</v>
+        <v>-4e-21</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>3966608.499661189</v>
+        <v>3966608.499661194</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>12492.78092853941</v>
+        <v>12492.31061761172</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>12492.78092853941</v>
+        <v>12492.31061761172</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-12492.7809285338</v>
+        <v>-12492.31061761172</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3183.658523252279</v>
+        <v>3183.538669282045</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3183.658523252279</v>
+        <v>3183.538669282045</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>487.2945791878016</v>
+        <v>487.414433158036</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1869,12 +1869,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>49596</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1909,19 +1909,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>39996.77419354839</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>31.71211550318614</v>
+        <v>125.964568212608</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>31.71211550318614</v>
+        <v>125.964568212608</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-31.71211550318614</v>
+        <v>-125.964568212608</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1934,12 +1934,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1949,44 +1949,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.3672154333303549</v>
+        <v>10068.978846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.000654398011699573</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.3672154333303549</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001156540143189488</v>
+        <v>31.71092164934791</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001156540143189488</v>
+        <v>31.71092164934791</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0005021421314899149</v>
+        <v>-31.71092164934791</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1999,12 +1999,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2018,40 +2018,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3672154333303549</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>0.000654398011699573</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3672154333303549</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.149486754139332e-09</v>
+        <v>0.001156496603366707</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.149486754139332e-09</v>
+        <v>0.001156496603366707</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.149486754139332e-09</v>
+        <v>-0.0005020985916671342</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2064,12 +2064,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2104,19 +2104,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>3.149368186620571e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>3.149368186620571e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>-3.149368186620571e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2129,12 +2129,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2194,12 +2194,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2209,26 +2209,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>0</v>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8588504.476194315</v>
+        <v>8586100.807660563</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="16">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-6188075.871421805</v>
+        <v>-6188058.353185593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>9534049.062243789</v>
+        <v>9531627.875473827</v>
       </c>
     </row>
     <row r="19">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-3345973.190821985</v>
+        <v>-3343569.522288233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>239722.7571465833</v>
+        <v>242126.4256803349</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:38+00:00</t>
+          <t>2026-07-31T00:12:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>812729.8191806873</v>
+        <v>812145.9731719492</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>812729.8191806873</v>
+        <v>812145.9731719492</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>180741.7411251486</v>
+        <v>181325.5871338868</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>791118.590882017</v>
+        <v>790550.2698719788</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>791118.590882017</v>
+        <v>790550.2698719788</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-536320.3902494919</v>
+        <v>-535752.0692394535</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>405737.526010569</v>
+        <v>405446.0537038245</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>405737.526010569</v>
+        <v>405446.0537038245</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>90231.34768807696</v>
+        <v>90522.81999482136</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>319682.5102507983</v>
+        <v>319452.8578456958</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>319682.5102507983</v>
+        <v>319452.8578456958</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>133422.7897492017</v>
+        <v>133652.4421543042</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>237121.9174690625</v>
+        <v>236951.5746542286</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>237121.9174690625</v>
+        <v>236951.5746542286</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>32211.14724888539</v>
+        <v>32381.49006371924</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>228589.5881358311</v>
+        <v>228425.3747459413</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>228589.5881358311</v>
+        <v>228425.3747459413</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>43984.88871086163</v>
+        <v>44149.10210075145</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>157468.4093310286</v>
+        <v>157355.2877251511</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>157468.4093310286</v>
+        <v>157355.2877251511</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231641.4906689714</v>
+        <v>231754.6122748489</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>123464.0815510022</v>
+        <v>123375.3878553423</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>123464.0815510022</v>
+        <v>123375.3878553423</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-171977.8845777201</v>
+        <v>-171889.1908820603</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>78815.92468452427</v>
+        <v>78759.30517584369</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>78815.92468452427</v>
+        <v>78759.30517584369</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67603.57673652428</v>
+        <v>-67546.9572278437</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>78737.87086205014</v>
+        <v>78681.30742540192</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>78737.87086205014</v>
+        <v>78681.30742540192</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78458.06931515611</v>
+        <v>-78401.5058785079</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>78678.67467484385</v>
+        <v>78622.15376334582</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>78678.67467484385</v>
+        <v>78622.15376334582</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-4612.526554804812</v>
+        <v>-4556.00564330679</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17994.75185631512</v>
+        <v>17981.82484933003</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17994.75185631512</v>
+        <v>17981.82484933003</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>299.4515655521261</v>
+        <v>312.3785725372201</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>12492.31061761172</v>
+        <v>12483.33643514434</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>12492.31061761172</v>
+        <v>12483.33643514434</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-12492.31061761172</v>
+        <v>-12483.33643514434</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3183.538669282045</v>
+        <v>3181.251689892513</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3183.538669282045</v>
+        <v>3181.251689892513</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>487.414433158036</v>
+        <v>489.7014125475674</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1915,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>125.964568212608</v>
+        <v>125.8740782260741</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>125.964568212608</v>
+        <v>125.8740782260741</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-125.964568212608</v>
+        <v>-125.8740782260741</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.71092164934791</v>
+        <v>31.68814126821579</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.71092164934791</v>
+        <v>31.68814126821579</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.71092164934791</v>
+        <v>-31.68814126821579</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001156496603366707</v>
+        <v>0.00115566580337628</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001156496603366707</v>
+        <v>0.00115566580337628</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0005020985916671342</v>
+        <v>-0.0005012677916767074</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2110,13 +2110,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.149368186620571e-09</v>
+        <v>3.147105754503021e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.149368186620571e-09</v>
+        <v>3.147105754503021e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.149368186620571e-09</v>
+        <v>-3.147105754503021e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.03689032258064516</v>
+        <v>0.03685483870967742</v>
       </c>
     </row>
     <row r="10">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.03732734186107307</v>
+        <v>0.03729777196859994</v>
       </c>
     </row>
     <row r="11">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03747483383441957</v>
+        <v>0.03744741878907706</v>
       </c>
     </row>
     <row r="12">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-20.35412891753571</v>
+        <v>-20.62827937096083</v>
       </c>
     </row>
     <row r="13">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>178277.9868267714</v>
+        <v>180681.655360523</v>
       </c>
     </row>
     <row r="15">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="17">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>178277.9868267714</v>
+        <v>180681.655360523</v>
       </c>
     </row>
     <row r="19">
@@ -3032,7 +3032,7 @@
         <v>997432546.824102</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3104672.504638677</v>
+        <v>3102268.836104926</v>
       </c>
     </row>
     <row r="21">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="25">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8588504.476194315</v>
+        <v>8586100.807660563</v>
       </c>
     </row>
     <row r="28">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9534049.062243789</v>
+        <v>9531627.875473827</v>
       </c>
     </row>
     <row r="31">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="32">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-6188075.871421805</v>
+        <v>-6188058.353185593</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -3806,16 +3806,16 @@
         <v>4</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>97975.47676751614</v>
+        <v>97761.31470851351</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>322195.4437217471</v>
+        <v>321975.3406253316</v>
       </c>
     </row>
     <row r="11">
@@ -3855,16 +3855,16 @@
         <v>4</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>98055.62136761917</v>
+        <v>97841.28412260936</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>322301.8744925075</v>
+        <v>322081.771396092</v>
       </c>
     </row>
     <row r="12">
@@ -3904,16 +3904,16 @@
         <v>4</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>98034.80773212721</v>
+        <v>97820.51598310456</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>322301.8744925075</v>
+        <v>322081.771396092</v>
       </c>
     </row>
     <row r="13">
@@ -3953,16 +3953,16 @@
         <v>4</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>103077.0320153224</v>
+        <v>102856.9289189069</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>327516.9903662701</v>
+        <v>327296.8872698547</v>
       </c>
     </row>
     <row r="14">
@@ -4002,16 +4002,16 @@
         <v>4</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>103077.0320153224</v>
+        <v>102856.9289189069</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>327516.9903662701</v>
+        <v>327296.8872698547</v>
       </c>
     </row>
     <row r="15">
@@ -4051,16 +4051,16 @@
         <v>4</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>103077.0320153224</v>
+        <v>102856.9289189069</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>327516.9903662701</v>
+        <v>327296.8872698547</v>
       </c>
     </row>
     <row r="16">
@@ -4198,16 +4198,16 @@
         <v>4</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>110100.399375221</v>
+        <v>109880.2962788055</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>323998.7001002377</v>
+        <v>323778.5970038222</v>
       </c>
     </row>
     <row r="19">
@@ -4247,16 +4247,16 @@
         <v>4</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>110187.7240966493</v>
+        <v>109967.6210002338</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>318784.2969737265</v>
+        <v>318564.1938773111</v>
       </c>
     </row>
     <row r="20">
@@ -4296,16 +4296,16 @@
         <v>4</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>112827.7753732605</v>
+        <v>112607.672276845</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>316122.6261382353</v>
+        <v>315902.5230418197</v>
       </c>
     </row>
     <row r="21">
@@ -4345,16 +4345,16 @@
         <v>4</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>112827.7753732605</v>
+        <v>112607.672276845</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>316122.6261382353</v>
+        <v>315902.5230418197</v>
       </c>
     </row>
     <row r="22">
@@ -4394,16 +4394,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>112827.7753732605</v>
+        <v>112607.672276845</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>316122.6261382353</v>
+        <v>315902.5230418197</v>
       </c>
     </row>
     <row r="23">
@@ -4492,16 +4492,16 @@
         <v>4</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0367</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03726825040376996</v>
+        <v>0.03718491707043663</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>112627.8105663799</v>
+        <v>112407.6721995111</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>305358.2933454882</v>
+        <v>305138.1549786194</v>
       </c>
     </row>
     <row r="25">
@@ -4541,16 +4541,16 @@
         <v>4</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0365</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03726825040376996</v>
+        <v>0.03701825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>110481.0523904593</v>
+        <v>109820.5843690742</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>297909.1428343162</v>
+        <v>297248.6748129312</v>
       </c>
     </row>
     <row r="26">
@@ -4933,16 +4933,16 @@
         <v>4</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>108960.0649366465</v>
+        <v>109180.2033563618</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>273162.9438668333</v>
+        <v>273383.0822865487</v>
       </c>
     </row>
     <row r="34">
@@ -4982,16 +4982,16 @@
         <v>4</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>109478.4706372722</v>
+        <v>109698.6090569876</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>273688.4873327413</v>
+        <v>273908.6257524567</v>
       </c>
     </row>
     <row r="35">
@@ -5031,16 +5031,16 @@
         <v>4</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>110004.0141031801</v>
+        <v>110224.1525228955</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>274214.0307986492</v>
+        <v>274434.1692183646</v>
       </c>
     </row>
     <row r="36">
@@ -5080,16 +5080,16 @@
         <v>4</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>110319.3401827249</v>
+        <v>110539.4786024403</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>274529.356878194</v>
+        <v>274749.4952979094</v>
       </c>
     </row>
     <row r="38">
@@ -5111,10 +5111,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="10" t="n">
-        <v>3345973.190821985</v>
+        <v>3343569.522288233</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>9534049.062243789</v>
+        <v>9531627.875473827</v>
       </c>
     </row>
   </sheetData>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -2918,7 +2918,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/reports/grove/2026-05/grove_settlement_may_2026.xlsx
+++ b/reports/grove/2026-05/grove_settlement_may_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3585695.947968568</v>
+        <v>3713239.05578596</v>
       </c>
     </row>
     <row r="5">
@@ -515,168 +515,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>3678175.065050077</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>18585.45388687248</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>3824303.626754341</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3343569.522288233</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>5242531.28537233</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>8586100.807660563</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3343569.522288233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3343569.522288233</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-6188058.353185593</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>9531627.875473827</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>3585695.947968568</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3713239.05578596</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-3343569.522288233</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
-        <v>242126.4256803349</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-01 → 2026-05-31 (31 days)</t>
-        </is>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
+        <v>369669.5334977265</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=86865826, base=46741326, ethereum=25218797, monad=78309381, plume=71786194</t>
+          <t>2026-05-01 → 2026-05-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-31T00:12:46+00:00</t>
+          <t>avalanche_c=86865826, base=46741326, ethereum=25218797, monad=78309381, plume=71786194</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:23+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
@@ -693,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1001,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>812145.9731719492</v>
+        <v>812223.7611216932</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>812145.9731719492</v>
+        <v>812223.7611216932</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>181325.5871338868</v>
+        <v>181247.7991841428</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>790550.2698719788</v>
+        <v>790625.9893690818</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>790550.2698719788</v>
+        <v>790625.9893690818</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-535752.0692394535</v>
+        <v>-535827.7887365567</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>405446.0537038245</v>
+        <v>405484.8876305954</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>405446.0537038245</v>
+        <v>405484.8876305954</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>90522.81999482136</v>
+        <v>90483.98606805052</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>319452.8578456958</v>
+        <v>319483.4552797441</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>319452.8578456958</v>
+        <v>319483.4552797441</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>133652.4421543042</v>
+        <v>133621.8447202559</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>236951.5746542286</v>
+        <v>236974.2700535655</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>236951.5746542286</v>
+        <v>236974.2700535655</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>32381.49006371924</v>
+        <v>32358.79466438239</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>228425.3747459413</v>
+        <v>228447.2534994634</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>228425.3747459413</v>
+        <v>228447.2534994634</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>44149.10210075145</v>
+        <v>44127.22334722937</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>157355.2877251511</v>
+        <v>157370.3593324949</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>157355.2877251511</v>
+        <v>157370.3593324949</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231754.6122748489</v>
+        <v>231739.5406675051</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1433,40 +1443,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>50865822.2173752</v>
+        <v>50783448.05845664</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32754774.88723497</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-18126183.27598623</v>
+        <v>-18028673.17122167</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-48513.80302671796</v>
+        <v>79029.30479067359</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>-48513.80302671796</v>
+        <v>79029.30479067359</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>39202809.65417551</v>
+        <v>39101059.36425512</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>123375.3878553423</v>
+        <v>123066.9552486809</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>123375.3878553423</v>
+        <v>123066.9552486809</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-171889.1908820603</v>
+        <v>-44037.65045800726</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1525,13 +1535,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>78759.30517584369</v>
+        <v>78766.84880109737</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>78759.30517584369</v>
+        <v>78766.84880109737</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-67546.9572278437</v>
+        <v>-67554.50085309737</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1590,13 +1600,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>78681.30742540192</v>
+        <v>78688.84357997261</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>78681.30742540192</v>
+        <v>78688.84357997261</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-78401.5058785079</v>
+        <v>-78409.0420330786</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1655,13 +1665,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>78622.15376334582</v>
+        <v>78629.68425213445</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>78622.15376334582</v>
+        <v>78629.68425213445</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-4556.00564330679</v>
+        <v>-4563.536132095423</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1720,13 +1730,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17981.82484933003</v>
+        <v>17983.54716198551</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17981.82484933003</v>
+        <v>17983.54716198551</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>312.3785725372201</v>
+        <v>310.6562598817485</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1785,13 +1795,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>12483.33643514434</v>
+        <v>12484.53209846021</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>12483.33643514434</v>
+        <v>12484.53209846021</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-12483.33643514434</v>
+        <v>-12484.53209846021</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1850,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>3181.251689892513</v>
+        <v>3181.556392562662</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>3181.251689892513</v>
+        <v>3181.556392562662</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>489.7014125475674</v>
+        <v>489.3967098774185</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1915,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>125.8740782260741</v>
+        <v>125.8861345395873</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>125.8740782260741</v>
+        <v>125.8861345395873</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-125.8740782260741</v>
+        <v>-125.8861345395873</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1980,13 +1990,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>31.68814126821579</v>
+        <v>31.69117638212619</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>31.68814126821579</v>
+        <v>31.69117638212619</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-31.68814126821579</v>
+        <v>-31.69117638212619</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2045,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.00115566580337628</v>
+        <v>0.001155776493912715</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.00115566580337628</v>
+        <v>0.001155776493912715</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0005012677916767074</v>
+        <v>-0.0005013784822131424</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2110,13 +2120,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.147105754503021e-09</v>
+        <v>3.147407186649898e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.147105754503021e-09</v>
+        <v>3.147407186649898e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.147105754503021e-09</v>
+        <v>-3.147407186649898e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2783,59 +2793,189 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -2928,7 +3068,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (tbill_3m), period avg</t>
+          <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
